--- a/wayforge/docs/M1_Technical_Deliverable_Plan_Template.xlsx
+++ b/wayforge/docs/M1_Technical_Deliverable_Plan_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joel\Documents\GitHub\wf-wayforge\wayforge\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA65E49-0D9E-44AE-8EB6-E51F2FB9D3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32E7EE8-3223-46D2-B854-7030C3E4DD8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="218">
   <si>
     <t>MILESTONE 1 TECHNICAL DELIVERABLE PLAN - TEAM PLANNING SHEET</t>
   </si>
@@ -669,6 +669,18 @@
   </si>
   <si>
     <t>F01, F02, F03</t>
+  </si>
+  <si>
+    <t>SCRUM-10 (SCRUM-97), SCRUM-11 (SCRUM-134)</t>
+  </si>
+  <si>
+    <t>SCRUM-8 (SCRUM-43, 46, 49)</t>
+  </si>
+  <si>
+    <t>SCRUM-8 (SCRUM-70, 76)</t>
+  </si>
+  <si>
+    <t>SCRUM-10 (SCRUM-92)</t>
   </si>
 </sst>
 </file>
@@ -959,53 +971,53 @@
     <xf numFmtId="0" fontId="14" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1324,60 +1336,60 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:12" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
     </row>
     <row r="3" spans="3:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="27"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="31"/>
     </row>
     <row r="5" spans="3:12" ht="214" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
     </row>
     <row r="7" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="21"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="23"/>
     </row>
     <row r="8" spans="3:12" ht="38.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C8" s="1" t="s">
@@ -1459,7 +1471,9 @@
       <c r="H11" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="6"/>
+      <c r="I11" s="6" t="s">
+        <v>215</v>
+      </c>
       <c r="J11" s="15" t="s">
         <v>28</v>
       </c>
@@ -1521,7 +1535,9 @@
       <c r="H13" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="6"/>
+      <c r="I13" s="6" t="s">
+        <v>214</v>
+      </c>
       <c r="J13" s="15" t="s">
         <v>42</v>
       </c>
@@ -1551,7 +1567,9 @@
       <c r="H14" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I14" s="6"/>
+      <c r="I14" s="6" t="s">
+        <v>216</v>
+      </c>
       <c r="J14" s="15" t="s">
         <v>48</v>
       </c>
@@ -1581,7 +1599,9 @@
       <c r="H15" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="6"/>
+      <c r="I15" s="6" t="s">
+        <v>217</v>
+      </c>
       <c r="J15" s="15" t="s">
         <v>54</v>
       </c>
@@ -1657,353 +1677,371 @@
       <c r="L18" s="6"/>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="21"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="23"/>
     </row>
     <row r="21" spans="3:12" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="21"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="23"/>
     </row>
     <row r="22" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C22" s="8">
         <v>1</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="21"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="23"/>
     </row>
     <row r="23" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C23" s="8">
         <v>2</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="21"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="23"/>
     </row>
     <row r="24" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C24" s="8">
         <v>3</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="21"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="23"/>
     </row>
     <row r="25" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C25" s="8">
         <v>4</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="21"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="23"/>
     </row>
     <row r="26" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C26" s="8">
         <v>5</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="21"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="23"/>
     </row>
     <row r="27" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C27" s="8">
         <v>6</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="21"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="23"/>
     </row>
     <row r="28" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C28" s="8">
         <v>7</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="21"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="23"/>
     </row>
     <row r="29" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C29" s="8">
         <v>8</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="21"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="23"/>
     </row>
     <row r="30" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C30" s="8">
         <v>9</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="21"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="23"/>
     </row>
     <row r="31" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C31" s="8">
         <v>10</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="21"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="23"/>
     </row>
     <row r="32" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C32" s="8">
         <v>11</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="21"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="23"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C34" s="28" t="s">
+      <c r="C34" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="21"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="23"/>
     </row>
     <row r="35" spans="3:12" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C35" s="22" t="s">
+      <c r="C35" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="D35" s="21"/>
-      <c r="E35" s="24" t="s">
+      <c r="D35" s="23"/>
+      <c r="E35" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="21"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="23"/>
     </row>
     <row r="36" spans="3:12" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="D36" s="21"/>
-      <c r="E36" s="24" t="s">
+      <c r="D36" s="23"/>
+      <c r="E36" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-      <c r="K36" s="20"/>
-      <c r="L36" s="21"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="23"/>
     </row>
     <row r="37" spans="3:12" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="22" t="s">
+      <c r="C37" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="D37" s="21"/>
-      <c r="E37" s="24" t="s">
+      <c r="D37" s="23"/>
+      <c r="E37" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
-      <c r="L37" s="21"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="23"/>
     </row>
     <row r="38" spans="3:12" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C38" s="22" t="s">
+      <c r="C38" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="21"/>
-      <c r="E38" s="24" t="s">
+      <c r="D38" s="23"/>
+      <c r="E38" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="20"/>
-      <c r="L38" s="21"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="23"/>
     </row>
     <row r="39" spans="3:12" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C39" s="22" t="s">
+      <c r="C39" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D39" s="21"/>
-      <c r="E39" s="24" t="s">
+      <c r="D39" s="23"/>
+      <c r="E39" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="20"/>
-      <c r="K39" s="20"/>
-      <c r="L39" s="21"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="23"/>
     </row>
     <row r="40" spans="3:12" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="D40" s="21"/>
-      <c r="E40" s="24" t="s">
+      <c r="D40" s="23"/>
+      <c r="E40" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="20"/>
-      <c r="L40" s="21"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="23"/>
     </row>
     <row r="41" spans="3:12" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C41" s="22" t="s">
+      <c r="C41" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="D41" s="21"/>
-      <c r="E41" s="24" t="s">
+      <c r="D41" s="23"/>
+      <c r="E41" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="21"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="23"/>
     </row>
     <row r="42" spans="3:12" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="21"/>
-      <c r="E42" s="24" t="s">
+      <c r="D42" s="23"/>
+      <c r="E42" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="20"/>
-      <c r="K42" s="20"/>
-      <c r="L42" s="21"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C7:L7"/>
+    <mergeCell ref="E42:L42"/>
+    <mergeCell ref="E39:L39"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:L35"/>
+    <mergeCell ref="D28:L28"/>
+    <mergeCell ref="C3:L3"/>
+    <mergeCell ref="E38:L38"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C34:L34"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="D25:L25"/>
+    <mergeCell ref="E41:L41"/>
+    <mergeCell ref="D31:L31"/>
+    <mergeCell ref="E37:L37"/>
+    <mergeCell ref="D27:L27"/>
+    <mergeCell ref="D32:L32"/>
     <mergeCell ref="C2:L2"/>
     <mergeCell ref="D30:L30"/>
     <mergeCell ref="C5:L5"/>
@@ -2020,24 +2058,6 @@
     <mergeCell ref="D22:L22"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C21:L21"/>
-    <mergeCell ref="C3:L3"/>
-    <mergeCell ref="E38:L38"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C34:L34"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="D25:L25"/>
-    <mergeCell ref="E41:L41"/>
-    <mergeCell ref="D31:L31"/>
-    <mergeCell ref="E37:L37"/>
-    <mergeCell ref="D27:L27"/>
-    <mergeCell ref="D32:L32"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C7:L7"/>
-    <mergeCell ref="E42:L42"/>
-    <mergeCell ref="E39:L39"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:L35"/>
-    <mergeCell ref="D28:L28"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="K11:K18" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -2062,40 +2082,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:7" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="21"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="23"/>
     </row>
     <row r="5" spans="3:7" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="21"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="23"/>
     </row>
     <row r="7" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="21"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="23"/>
     </row>
     <row r="8" spans="3:7" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C8" s="10" t="s">
@@ -2387,13 +2407,13 @@
       </c>
     </row>
     <row r="26" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="21"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="23"/>
     </row>
     <row r="27" spans="3:7" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C27" s="10" t="s">
@@ -2413,11 +2433,11 @@
       <c r="D28" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="E28" s="33" t="s">
+      <c r="E28" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="F28" s="20"/>
-      <c r="G28" s="21"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="23"/>
     </row>
     <row r="29" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C29" s="11" t="s">
@@ -2426,11 +2446,11 @@
       <c r="D29" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="E29" s="33" t="s">
+      <c r="E29" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="F29" s="20"/>
-      <c r="G29" s="21"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="23"/>
     </row>
     <row r="30" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C30" s="11" t="s">
@@ -2439,11 +2459,11 @@
       <c r="D30" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="E30" s="33" t="s">
+      <c r="E30" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="F30" s="20"/>
-      <c r="G30" s="21"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="23"/>
     </row>
     <row r="31" spans="3:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C31" s="11" t="s">
@@ -2452,11 +2472,11 @@
       <c r="D31" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="E31" s="33" t="s">
+      <c r="E31" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="F31" s="20"/>
-      <c r="G31" s="21"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="23"/>
     </row>
     <row r="32" spans="3:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C32" s="11" t="s">
@@ -2465,11 +2485,11 @@
       <c r="D32" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="E32" s="33" t="s">
+      <c r="E32" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="F32" s="20"/>
-      <c r="G32" s="21"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="23"/>
     </row>
     <row r="33" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C33" s="11" t="s">
@@ -2478,20 +2498,20 @@
       <c r="D33" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="E33" s="33" t="s">
+      <c r="E33" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="F33" s="20"/>
-      <c r="G33" s="21"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="23"/>
     </row>
     <row r="35" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C35" s="28" t="s">
+      <c r="C35" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="21"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="23"/>
     </row>
     <row r="36" spans="3:7" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C36" s="10" t="s">
@@ -2505,29 +2525,29 @@
       <c r="C37" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="D37" s="24" t="s">
+      <c r="D37" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="21"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="23"/>
     </row>
     <row r="38" spans="3:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C38" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="D38" s="24" t="s">
+      <c r="D38" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="21"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="23"/>
     </row>
     <row r="39" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="D39" s="34"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
     </row>
     <row r="40" spans="3:7" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C40" s="10" t="s">
@@ -2541,143 +2561,140 @@
       <c r="C41" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="D41" s="24" t="s">
+      <c r="D41" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="21"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="23"/>
     </row>
     <row r="42" spans="3:7" ht="49" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C42" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="D42" s="24" t="s">
+      <c r="D42" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="21"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="23"/>
     </row>
     <row r="43" spans="3:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C43" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="D43" s="24" t="s">
+      <c r="D43" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="21"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="23"/>
     </row>
     <row r="44" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C44" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="D44" s="24" t="s">
+      <c r="D44" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="21"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="23"/>
     </row>
     <row r="45" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="D45" s="34"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
     </row>
     <row r="46" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C46" s="28" t="s">
+      <c r="C46" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="21"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="23"/>
     </row>
     <row r="47" spans="3:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C47" s="36" t="s">
         <v>200</v>
       </c>
-      <c r="D47" s="21"/>
-      <c r="E47" s="24" t="s">
+      <c r="D47" s="23"/>
+      <c r="E47" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="F47" s="20"/>
-      <c r="G47" s="21"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="23"/>
     </row>
     <row r="48" spans="3:7" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C48" s="36" t="s">
         <v>202</v>
       </c>
-      <c r="D48" s="21"/>
-      <c r="E48" s="24" t="s">
+      <c r="D48" s="23"/>
+      <c r="E48" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="F48" s="20"/>
-      <c r="G48" s="21"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="23"/>
     </row>
     <row r="49" spans="3:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C49" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="D49" s="21"/>
-      <c r="E49" s="24" t="s">
+      <c r="D49" s="23"/>
+      <c r="E49" s="25" t="s">
         <v>204</v>
       </c>
-      <c r="F49" s="20"/>
-      <c r="G49" s="21"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="23"/>
     </row>
     <row r="50" spans="3:7" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C50" s="36" t="s">
         <v>205</v>
       </c>
-      <c r="D50" s="21"/>
-      <c r="E50" s="24" t="s">
+      <c r="D50" s="23"/>
+      <c r="E50" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="F50" s="20"/>
-      <c r="G50" s="21"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="23"/>
     </row>
     <row r="51" spans="3:7" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C51" s="36" t="s">
         <v>207</v>
       </c>
-      <c r="D51" s="21"/>
-      <c r="E51" s="24" t="s">
+      <c r="D51" s="23"/>
+      <c r="E51" s="25" t="s">
         <v>208</v>
       </c>
-      <c r="F51" s="20"/>
-      <c r="G51" s="21"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="23"/>
     </row>
     <row r="52" spans="3:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C52" s="36" t="s">
         <v>209</v>
       </c>
-      <c r="D52" s="21"/>
-      <c r="E52" s="24" t="s">
+      <c r="D52" s="23"/>
+      <c r="E52" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="F52" s="20"/>
-      <c r="G52" s="21"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="23"/>
     </row>
     <row r="53" spans="3:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C53" s="37" t="s">
+      <c r="C53" s="33" t="s">
         <v>211</v>
       </c>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="21"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="D43:G43"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="E30:G30"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="C51:D51"/>
     <mergeCell ref="E47:G47"/>
@@ -2694,6 +2711,11 @@
     <mergeCell ref="D44:G44"/>
     <mergeCell ref="C50:D50"/>
     <mergeCell ref="E32:G32"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="D43:G43"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="C3:G3"/>
     <mergeCell ref="C49:D49"/>
     <mergeCell ref="D45:G45"/>
     <mergeCell ref="C46:G46"/>
@@ -2705,8 +2727,6 @@
     <mergeCell ref="E28:G28"/>
     <mergeCell ref="D39:G39"/>
     <mergeCell ref="E31:G31"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="E30:G30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
